--- a/proyectos/p-webs-adsense/fabrica/productos/planificador-taxes-2026/planificador-taxes-2026.xlsx
+++ b/proyectos/p-webs-adsense/fabrica/productos/planificador-taxes-2026/planificador-taxes-2026.xlsx
@@ -165,7 +165,7 @@
     <numFmt numFmtId="170" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="171" formatCode="0.0&quot; % de tu ganancia&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -269,12 +269,18 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3B57"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000A1C22"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000A1C22"/>
+      <color rgb="001F3B57"/>
       <sz val="10"/>
     </font>
     <font>
@@ -392,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -472,22 +478,21 @@
     <xf numFmtId="171" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="19" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -509,14 +514,14 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="19" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -526,13 +531,17 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1368,60 +1377,60 @@
       <c r="D7" s="18" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>Deducción estándar · Soltero (single)</t>
         </is>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="51" t="n">
         <v>16100</v>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="52" t="inlineStr">
         <is>
           <t>IRS Rev. Proc. 2025-32 (ajustes por inflación del año fiscal 2026)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>Deducción estándar · Casado, declaración conjunta (married filing jointly)</t>
         </is>
       </c>
-      <c r="C9" s="50" t="n">
+      <c r="C9" s="51" t="n">
         <v>32200</v>
       </c>
-      <c r="D9" s="51" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>IRS Rev. Proc. 2025-32 (ajustes por inflación del año fiscal 2026)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>Deducción estándar · Cabeza de familia (head of household)</t>
         </is>
       </c>
-      <c r="C10" s="50" t="n">
+      <c r="C10" s="51" t="n">
         <v>24150</v>
       </c>
-      <c r="D10" s="51" t="inlineStr">
+      <c r="D10" s="52" t="inlineStr">
         <is>
           <t>IRS Rev. Proc. 2025-32 (ajustes por inflación del año fiscal 2026)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>Deducción estándar · Casado, declaración separada (married filing separately)</t>
         </is>
       </c>
-      <c r="C11" s="50" t="n">
+      <c r="C11" s="51" t="n">
         <v>16100</v>
       </c>
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D11" s="52" t="inlineStr">
         <is>
           <t>IRS Rev. Proc. 2025-32 (ajustes por inflación del año fiscal 2026)</t>
         </is>
@@ -1437,7 +1446,7 @@
       <c r="D12" s="18" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
         <is>
           <t>Base del self-employment tax (% de la ganancia)</t>
         </is>
@@ -1445,14 +1454,14 @@
       <c r="C13" s="38" t="n">
         <v>92.34999999999999</v>
       </c>
-      <c r="D13" s="51" t="inlineStr">
+      <c r="D13" s="52" t="inlineStr">
         <is>
           <t>IRS: Self-Employment Tax (Social Security and Medicare Taxes) e instrucciones del Schedule SE (Form 1040)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>Seguro Social del autónomo (%)</t>
         </is>
@@ -1460,14 +1469,14 @@
       <c r="C14" s="38" t="n">
         <v>12.4</v>
       </c>
-      <c r="D14" s="51" t="inlineStr">
+      <c r="D14" s="52" t="inlineStr">
         <is>
           <t>IRS: Self-Employment Tax (Social Security and Medicare Taxes) e instrucciones del Schedule SE (Form 1040)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
         <is>
           <t>Medicare del autónomo (%)</t>
         </is>
@@ -1475,29 +1484,29 @@
       <c r="C15" s="38" t="n">
         <v>2.9</v>
       </c>
-      <c r="D15" s="51" t="inlineStr">
+      <c r="D15" s="52" t="inlineStr">
         <is>
           <t>IRS: Self-Employment Tax (Social Security and Medicare Taxes) e instrucciones del Schedule SE (Form 1040)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="49" t="inlineStr">
+      <c r="B16" s="50" t="inlineStr">
         <is>
           <t>Ganancia mínima para pagar self-employment tax ($)</t>
         </is>
       </c>
-      <c r="C16" s="50" t="n">
+      <c r="C16" s="51" t="n">
         <v>400</v>
       </c>
-      <c r="D16" s="51" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>IRS: Self-Employment Tax (Social Security and Medicare Taxes) e instrucciones del Schedule SE (Form 1040)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>Parte deducible del self-employment tax (%)</t>
         </is>
@@ -1505,29 +1514,29 @@
       <c r="C17" s="38" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="51" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>IRS: Self-Employment Tax (Social Security and Medicare Taxes) e instrucciones del Schedule SE (Form 1040)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B18" s="50" t="inlineStr">
         <is>
           <t>Tope de salario del Seguro Social ($)</t>
         </is>
       </c>
-      <c r="C18" s="50" t="n">
+      <c r="C18" s="51" t="n">
         <v>184500</v>
       </c>
-      <c r="D18" s="51" t="inlineStr">
+      <c r="D18" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="49" t="inlineStr">
+      <c r="B19" s="50" t="inlineStr">
         <is>
           <t>Medicare adicional (%)</t>
         </is>
@@ -1535,82 +1544,82 @@
       <c r="C19" s="38" t="n">
         <v>0.9</v>
       </c>
-      <c r="D19" s="51" t="inlineStr">
+      <c r="D19" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="49" t="inlineStr">
+      <c r="B20" s="50" t="inlineStr">
         <is>
           <t>El empleador retiene el adicional por encima de ($)</t>
         </is>
       </c>
-      <c r="C20" s="50" t="n">
+      <c r="C20" s="51" t="n">
         <v>200000</v>
       </c>
-      <c r="D20" s="51" t="inlineStr">
+      <c r="D20" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="49" t="inlineStr">
+      <c r="B21" s="50" t="inlineStr">
         <is>
           <t>Umbral del Medicare adicional · Soltero (single)</t>
         </is>
       </c>
-      <c r="C21" s="50" t="n">
+      <c r="C21" s="51" t="n">
         <v>200000</v>
       </c>
-      <c r="D21" s="51" t="inlineStr">
+      <c r="D21" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="49" t="inlineStr">
+      <c r="B22" s="50" t="inlineStr">
         <is>
           <t>Umbral del Medicare adicional · Casado, declaración conjunta (married filing jointly)</t>
         </is>
       </c>
-      <c r="C22" s="50" t="n">
+      <c r="C22" s="51" t="n">
         <v>250000</v>
       </c>
-      <c r="D22" s="51" t="inlineStr">
+      <c r="D22" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="50" t="inlineStr">
         <is>
           <t>Umbral del Medicare adicional · Cabeza de familia (head of household)</t>
         </is>
       </c>
-      <c r="C23" s="50" t="n">
+      <c r="C23" s="51" t="n">
         <v>200000</v>
       </c>
-      <c r="D23" s="51" t="inlineStr">
+      <c r="D23" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="50" t="inlineStr">
         <is>
           <t>Umbral del Medicare adicional · Casado, declaración separada (married filing separately)</t>
         </is>
       </c>
-      <c r="C24" s="50" t="n">
+      <c r="C24" s="51" t="n">
         <v>125000</v>
       </c>
-      <c r="D24" s="51" t="inlineStr">
+      <c r="D24" s="52" t="inlineStr">
         <is>
           <t>SSA: 2026 COLA Fact Sheet (contribution and benefit base); IRS Topic 751 y Questions and answers for the Additional Medicare Tax</t>
         </is>
@@ -1626,7 +1635,7 @@
       <c r="D25" s="18" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="49" t="inlineStr">
+      <c r="B26" s="50" t="inlineStr">
         <is>
           <t>Deducción por ingreso de negocio (%)</t>
         </is>
@@ -1634,67 +1643,67 @@
       <c r="C26" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="D26" s="51" t="inlineStr">
+      <c r="D26" s="52" t="inlineStr">
         <is>
           <t>IRS: Qualified business income deduction</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="49" t="inlineStr">
+      <c r="B27" s="50" t="inlineStr">
         <is>
           <t>Umbral (sin límites por debajo) · Soltero (single)</t>
         </is>
       </c>
-      <c r="C27" s="50" t="n">
+      <c r="C27" s="51" t="n">
         <v>201750</v>
       </c>
-      <c r="D27" s="51" t="inlineStr">
+      <c r="D27" s="52" t="inlineStr">
         <is>
           <t>IRS: Qualified business income deduction</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="49" t="inlineStr">
+      <c r="B28" s="50" t="inlineStr">
         <is>
           <t>Umbral (sin límites por debajo) · Casado, declaración conjunta (married filing jointly)</t>
         </is>
       </c>
-      <c r="C28" s="50" t="n">
+      <c r="C28" s="51" t="n">
         <v>403500</v>
       </c>
-      <c r="D28" s="51" t="inlineStr">
+      <c r="D28" s="52" t="inlineStr">
         <is>
           <t>IRS: Qualified business income deduction</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="50" t="inlineStr">
         <is>
           <t>Umbral (sin límites por debajo) · Cabeza de familia (head of household)</t>
         </is>
       </c>
-      <c r="C29" s="50" t="n">
+      <c r="C29" s="51" t="n">
         <v>201750</v>
       </c>
-      <c r="D29" s="51" t="inlineStr">
+      <c r="D29" s="52" t="inlineStr">
         <is>
           <t>IRS: Qualified business income deduction</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="49" t="inlineStr">
+      <c r="B30" s="50" t="inlineStr">
         <is>
           <t>Umbral (sin límites por debajo) · Casado, declaración separada (married filing separately)</t>
         </is>
       </c>
-      <c r="C30" s="50" t="n">
+      <c r="C30" s="51" t="n">
         <v>201775</v>
       </c>
-      <c r="D30" s="51" t="inlineStr">
+      <c r="D30" s="52" t="inlineStr">
         <is>
           <t>IRS: Qualified business income deduction</t>
         </is>
@@ -1710,67 +1719,67 @@
       <c r="D31" s="18" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr">
         <is>
           <t>Por hijo menor de 17 ($)</t>
         </is>
       </c>
-      <c r="C32" s="50" t="n">
+      <c r="C32" s="51" t="n">
         <v>2200</v>
       </c>
-      <c r="D32" s="51" t="inlineStr">
+      <c r="D32" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="49" t="inlineStr">
+      <c r="B33" s="50" t="inlineStr">
         <is>
           <t>Por otro dependiente ($)</t>
         </is>
       </c>
-      <c r="C33" s="50" t="n">
+      <c r="C33" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="D33" s="51" t="inlineStr">
+      <c r="D33" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="49" t="inlineStr">
+      <c r="B34" s="50" t="inlineStr">
         <is>
           <t>Parte reembolsable máxima por hijo (ACTC) ($)</t>
         </is>
       </c>
-      <c r="C34" s="50" t="n">
+      <c r="C34" s="51" t="n">
         <v>1700</v>
       </c>
-      <c r="D34" s="51" t="inlineStr">
+      <c r="D34" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="49" t="inlineStr">
+      <c r="B35" s="50" t="inlineStr">
         <is>
           <t>ACTC: ingreso ganado a partir de ($)</t>
         </is>
       </c>
-      <c r="C35" s="50" t="n">
+      <c r="C35" s="51" t="n">
         <v>2500</v>
       </c>
-      <c r="D35" s="51" t="inlineStr">
+      <c r="D35" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="B36" s="49" t="inlineStr">
+      <c r="B36" s="50" t="inlineStr">
         <is>
           <t>ACTC: % del ingreso ganado por encima</t>
         </is>
@@ -1778,82 +1787,82 @@
       <c r="C36" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="D36" s="51" t="inlineStr">
+      <c r="D36" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="49" t="inlineStr">
+      <c r="B37" s="50" t="inlineStr">
         <is>
           <t>Reducción por cada 1.000 $ por encima del umbral ($)</t>
         </is>
       </c>
-      <c r="C37" s="50" t="n">
+      <c r="C37" s="51" t="n">
         <v>50</v>
       </c>
-      <c r="D37" s="51" t="inlineStr">
+      <c r="D37" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="50" t="inlineStr">
         <is>
           <t>Umbral de reducción · Soltero (single)</t>
         </is>
       </c>
-      <c r="C38" s="50" t="n">
+      <c r="C38" s="51" t="n">
         <v>200000</v>
       </c>
-      <c r="D38" s="51" t="inlineStr">
+      <c r="D38" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="B39" s="49" t="inlineStr">
+      <c r="B39" s="50" t="inlineStr">
         <is>
           <t>Umbral de reducción · Casado, declaración conjunta (married filing jointly)</t>
         </is>
       </c>
-      <c r="C39" s="50" t="n">
+      <c r="C39" s="51" t="n">
         <v>400000</v>
       </c>
-      <c r="D39" s="51" t="inlineStr">
+      <c r="D39" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="49" t="inlineStr">
+      <c r="B40" s="50" t="inlineStr">
         <is>
           <t>Umbral de reducción · Cabeza de familia (head of household)</t>
         </is>
       </c>
-      <c r="C40" s="50" t="n">
+      <c r="C40" s="51" t="n">
         <v>200000</v>
       </c>
-      <c r="D40" s="51" t="inlineStr">
+      <c r="D40" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="49" t="inlineStr">
+      <c r="B41" s="50" t="inlineStr">
         <is>
           <t>Umbral de reducción · Casado, declaración separada (married filing separately)</t>
         </is>
       </c>
-      <c r="C41" s="50" t="n">
+      <c r="C41" s="51" t="n">
         <v>200000</v>
       </c>
-      <c r="D41" s="51" t="inlineStr">
+      <c r="D41" s="52" t="inlineStr">
         <is>
           <t>IRS: Child Tax Credit y Rev. Proc. 2025-32, sección 4.05</t>
         </is>
@@ -1869,22 +1878,22 @@
       <c r="D42" s="18" t="n"/>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="B43" s="49" t="inlineStr">
+      <c r="B43" s="50" t="inlineStr">
         <is>
           <t>Hay que hacer pagos si vas a deber al menos ($)</t>
         </is>
       </c>
-      <c r="C43" s="50" t="n">
+      <c r="C43" s="51" t="n">
         <v>1000</v>
       </c>
-      <c r="D43" s="51" t="inlineStr">
+      <c r="D43" s="52" t="inlineStr">
         <is>
           <t>IRS: Form 1040-ES (2026) y Publicación 505</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="B44" s="49" t="inlineStr">
+      <c r="B44" s="50" t="inlineStr">
         <is>
           <t>Puerto seguro: % del impuesto de este año</t>
         </is>
@@ -1892,14 +1901,14 @@
       <c r="C44" s="38" t="n">
         <v>90</v>
       </c>
-      <c r="D44" s="51" t="inlineStr">
+      <c r="D44" s="52" t="inlineStr">
         <is>
           <t>IRS: Form 1040-ES (2026) y Publicación 505</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="B45" s="49" t="inlineStr">
+      <c r="B45" s="50" t="inlineStr">
         <is>
           <t>Puerto seguro: % del impuesto del año pasado</t>
         </is>
@@ -1907,14 +1916,14 @@
       <c r="C45" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="D45" s="51" t="inlineStr">
+      <c r="D45" s="52" t="inlineStr">
         <is>
           <t>IRS: Form 1040-ES (2026) y Publicación 505</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="B46" s="49" t="inlineStr">
+      <c r="B46" s="50" t="inlineStr">
         <is>
           <t>Puerto seguro con AGI alto: % del año pasado</t>
         </is>
@@ -1922,37 +1931,37 @@
       <c r="C46" s="38" t="n">
         <v>110</v>
       </c>
-      <c r="D46" s="51" t="inlineStr">
+      <c r="D46" s="52" t="inlineStr">
         <is>
           <t>IRS: Form 1040-ES (2026) y Publicación 505</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="B47" s="49" t="inlineStr">
+      <c r="B47" s="50" t="inlineStr">
         <is>
           <t>AGI alto a partir de ($)</t>
         </is>
       </c>
-      <c r="C47" s="50" t="n">
+      <c r="C47" s="51" t="n">
         <v>150000</v>
       </c>
-      <c r="D47" s="51" t="inlineStr">
+      <c r="D47" s="52" t="inlineStr">
         <is>
           <t>IRS: Form 1040-ES (2026) y Publicación 505</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="B48" s="49" t="inlineStr">
+      <c r="B48" s="50" t="inlineStr">
         <is>
           <t>AGI alto, casado por separado ($)</t>
         </is>
       </c>
-      <c r="C48" s="50" t="n">
+      <c r="C48" s="51" t="n">
         <v>75000</v>
       </c>
-      <c r="D48" s="51" t="inlineStr">
+      <c r="D48" s="52" t="inlineStr">
         <is>
           <t>IRS: Form 1040-ES (2026) y Publicación 505</t>
         </is>
@@ -2323,13 +2332,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C7" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="53" t="n">
+      <c r="C7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="54">
         <f>D7</f>
         <v/>
       </c>
@@ -2353,58 +2362,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="54" t="n">
+      <c r="K7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2414,13 +2423,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C8" s="52" t="n">
+      <c r="C8" s="53" t="n">
         <v>12400</v>
       </c>
-      <c r="D8" s="53" t="n">
+      <c r="D8" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="54">
         <f>D8-D7</f>
         <v/>
       </c>
@@ -2444,7 +2453,7 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K8" s="54" t="n">
+      <c r="K8" s="55" t="n">
         <v>2.5</v>
       </c>
       <c r="L8" s="38" t="inlineStr">
@@ -2467,43 +2476,43 @@
           <t>federal</t>
         </is>
       </c>
-      <c r="P8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="54" t="n">
+      <c r="P8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2513,13 +2522,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="53" t="n">
         <v>50400</v>
       </c>
-      <c r="D9" s="53" t="n">
+      <c r="D9" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="54">
         <f>D9-D8</f>
         <v/>
       </c>
@@ -2543,58 +2552,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="54" t="n">
+      <c r="K9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="55" t="n">
         <v>5900</v>
       </c>
-      <c r="M9" s="54" t="n">
+      <c r="M9" s="55" t="n">
         <v>11800</v>
       </c>
-      <c r="N9" s="54" t="n">
+      <c r="N9" s="55" t="n">
         <v>11800</v>
       </c>
-      <c r="O9" s="54" t="n">
+      <c r="O9" s="55" t="n">
         <v>5900</v>
       </c>
-      <c r="P9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="54" t="n">
+      <c r="P9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="55" t="n">
         <v>1000000</v>
       </c>
-      <c r="W9" s="54" t="n">
+      <c r="W9" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="X9" s="54" t="n">
+      <c r="X9" s="55" t="n">
         <v>158</v>
       </c>
-      <c r="Y9" s="54" t="n">
+      <c r="Y9" s="55" t="n">
         <v>316</v>
       </c>
-      <c r="Z9" s="54" t="n">
+      <c r="Z9" s="55" t="n">
         <v>158</v>
       </c>
-      <c r="AA9" s="54" t="n">
+      <c r="AA9" s="55" t="n">
         <v>158</v>
       </c>
-      <c r="AB9" s="54" t="n">
+      <c r="AB9" s="55" t="n">
         <v>491</v>
       </c>
     </row>
@@ -2604,13 +2613,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="53" t="n">
         <v>105700</v>
       </c>
-      <c r="D10" s="53" t="n">
+      <c r="D10" s="54" t="n">
         <v>24</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="54">
         <f>D10-D9</f>
         <v/>
       </c>
@@ -2634,58 +2643,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K10" s="54" t="n">
+      <c r="K10" s="55" t="n">
         <v>3.99</v>
       </c>
-      <c r="L10" s="54" t="n">
+      <c r="L10" s="55" t="n">
         <v>12750</v>
       </c>
-      <c r="M10" s="54" t="n">
+      <c r="M10" s="55" t="n">
         <v>25500</v>
       </c>
-      <c r="N10" s="54" t="n">
+      <c r="N10" s="55" t="n">
         <v>19125</v>
       </c>
-      <c r="O10" s="54" t="n">
+      <c r="O10" s="55" t="n">
         <v>12750</v>
       </c>
-      <c r="P10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="54" t="n">
+      <c r="P10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2695,13 +2704,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C11" s="52" t="n">
+      <c r="C11" s="53" t="n">
         <v>201775</v>
       </c>
-      <c r="D11" s="53" t="n">
+      <c r="D11" s="54" t="n">
         <v>32</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="54">
         <f>D11-D10</f>
         <v/>
       </c>
@@ -2725,58 +2734,58 @@
           <t>federal_imponible</t>
         </is>
       </c>
-      <c r="K11" s="54" t="n">
+      <c r="K11" s="55" t="n">
         <v>4.4</v>
       </c>
-      <c r="L11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="54" t="n">
+      <c r="L11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2786,13 +2795,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C12" s="52" t="n">
+      <c r="C12" s="53" t="n">
         <v>256225</v>
       </c>
-      <c r="D12" s="53" t="n">
+      <c r="D12" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="54">
         <f>D12-D11</f>
         <v/>
       </c>
@@ -2816,58 +2825,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="54" t="n">
+      <c r="K12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2877,13 +2886,13 @@
           <t>FED|1</t>
         </is>
       </c>
-      <c r="C13" s="52" t="n">
+      <c r="C13" s="53" t="n">
         <v>640600</v>
       </c>
-      <c r="D13" s="53" t="n">
+      <c r="D13" s="54" t="n">
         <v>37</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="54">
         <f>D13-D12</f>
         <v/>
       </c>
@@ -2907,58 +2916,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="54" t="n">
+      <c r="K13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2968,13 +2977,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C14" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="53" t="n">
+      <c r="C14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="54">
         <f>D14</f>
         <v/>
       </c>
@@ -2998,58 +3007,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K14" s="54" t="n">
+      <c r="K14" s="55" t="n">
         <v>4.99</v>
       </c>
-      <c r="L14" s="54" t="n">
+      <c r="L14" s="55" t="n">
         <v>12000</v>
       </c>
-      <c r="M14" s="54" t="n">
+      <c r="M14" s="55" t="n">
         <v>24000</v>
       </c>
-      <c r="N14" s="54" t="n">
+      <c r="N14" s="55" t="n">
         <v>12000</v>
       </c>
-      <c r="O14" s="54" t="n">
+      <c r="O14" s="55" t="n">
         <v>12000</v>
       </c>
-      <c r="P14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="54" t="n">
+      <c r="P14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="55" t="n">
         <v>4000</v>
       </c>
-      <c r="V14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="54" t="n">
+      <c r="V14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3059,13 +3068,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C15" s="52" t="n">
+      <c r="C15" s="53" t="n">
         <v>24800</v>
       </c>
-      <c r="D15" s="53" t="n">
+      <c r="D15" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="54">
         <f>D15-D14</f>
         <v/>
       </c>
@@ -3089,58 +3098,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K15" s="54" t="n">
+      <c r="K15" s="55" t="n">
         <v>4.95</v>
       </c>
-      <c r="L15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="54" t="n">
+      <c r="L15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="55" t="n">
         <v>2925</v>
       </c>
-      <c r="Q15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="54" t="n">
+      <c r="Q15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3150,13 +3159,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C16" s="52" t="n">
+      <c r="C16" s="53" t="n">
         <v>100800</v>
       </c>
-      <c r="D16" s="53" t="n">
+      <c r="D16" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="54">
         <f>D16-D15</f>
         <v/>
       </c>
@@ -3180,58 +3189,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K16" s="54" t="n">
+      <c r="K16" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="L16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="54" t="n">
+      <c r="L16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="55" t="n">
         <v>4400</v>
       </c>
-      <c r="R16" s="54" t="n">
+      <c r="R16" s="55" t="n">
         <v>8800</v>
       </c>
-      <c r="S16" s="54" t="n">
+      <c r="S16" s="55" t="n">
         <v>6800</v>
       </c>
-      <c r="T16" s="54" t="n">
+      <c r="T16" s="55" t="n">
         <v>4400</v>
       </c>
-      <c r="U16" s="54" t="n">
+      <c r="U16" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="V16" s="54" t="n">
+      <c r="V16" s="55" t="n">
         <v>1107750</v>
       </c>
-      <c r="W16" s="54" t="n">
+      <c r="W16" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="X16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="54" t="n">
+      <c r="X16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3241,13 +3250,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C17" s="52" t="n">
+      <c r="C17" s="53" t="n">
         <v>211400</v>
       </c>
-      <c r="D17" s="53" t="n">
+      <c r="D17" s="54" t="n">
         <v>24</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="54">
         <f>D17-D16</f>
         <v/>
       </c>
@@ -3271,58 +3280,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="54" t="n">
+      <c r="K17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3332,13 +3341,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C18" s="52" t="n">
+      <c r="C18" s="53" t="n">
         <v>403550</v>
       </c>
-      <c r="D18" s="53" t="n">
+      <c r="D18" s="54" t="n">
         <v>32</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="54">
         <f>D18-D17</f>
         <v/>
       </c>
@@ -3362,58 +3371,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="54" t="n">
+      <c r="K18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="R18" s="54" t="n">
+      <c r="R18" s="55" t="n">
         <v>2000</v>
       </c>
-      <c r="S18" s="54" t="n">
+      <c r="S18" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="T18" s="54" t="n">
+      <c r="T18" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="U18" s="54" t="n">
+      <c r="U18" s="55" t="n">
         <v>1500</v>
       </c>
-      <c r="V18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="54" t="n">
+      <c r="V18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3423,13 +3432,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="53" t="n">
         <v>512450</v>
       </c>
-      <c r="D19" s="53" t="n">
+      <c r="D19" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="54">
         <f>D19-D18</f>
         <v/>
       </c>
@@ -3453,58 +3462,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="54" t="n">
+      <c r="K19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="55" t="n">
         <v>8000</v>
       </c>
-      <c r="M19" s="54" t="n">
+      <c r="M19" s="55" t="n">
         <v>16050</v>
       </c>
-      <c r="N19" s="54" t="n">
+      <c r="N19" s="55" t="n">
         <v>11200</v>
       </c>
-      <c r="O19" s="54" t="n">
+      <c r="O19" s="55" t="n">
         <v>8000</v>
       </c>
-      <c r="P19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="54" t="n">
+      <c r="P19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="V19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="54" t="n">
+      <c r="V19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3514,13 +3523,13 @@
           <t>FED|2</t>
         </is>
       </c>
-      <c r="C20" s="52" t="n">
+      <c r="C20" s="53" t="n">
         <v>768700</v>
       </c>
-      <c r="D20" s="53" t="n">
+      <c r="D20" s="54" t="n">
         <v>37</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="54">
         <f>D20-D19</f>
         <v/>
       </c>
@@ -3544,58 +3553,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="54" t="n">
+      <c r="K20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3605,13 +3614,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C21" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="53" t="n">
+      <c r="C21" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="54">
         <f>D21</f>
         <v/>
       </c>
@@ -3635,7 +3644,7 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K21" s="54" t="n">
+      <c r="K21" s="55" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="38" t="inlineStr">
@@ -3658,43 +3667,43 @@
           <t>federal</t>
         </is>
       </c>
-      <c r="P21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="54" t="n">
+      <c r="P21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3704,13 +3713,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="53" t="n">
         <v>17700</v>
       </c>
-      <c r="D22" s="53" t="n">
+      <c r="D22" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="54">
         <f>D22-D21</f>
         <v/>
       </c>
@@ -3734,58 +3743,58 @@
           <t>salario_bruto</t>
         </is>
       </c>
-      <c r="K22" s="54" t="n">
+      <c r="K22" s="55" t="n">
         <v>3.07</v>
       </c>
-      <c r="L22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="54" t="n">
+      <c r="L22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3795,13 +3804,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="53" t="n">
         <v>67450</v>
       </c>
-      <c r="D23" s="53" t="n">
+      <c r="D23" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="54">
         <f>D23-D22</f>
         <v/>
       </c>
@@ -3825,58 +3834,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="54" t="n">
+      <c r="K23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3886,13 +3895,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C24" s="52" t="n">
+      <c r="C24" s="53" t="n">
         <v>105700</v>
       </c>
-      <c r="D24" s="53" t="n">
+      <c r="D24" s="54" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="54">
         <f>D24-D23</f>
         <v/>
       </c>
@@ -3916,58 +3925,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="54" t="n">
+      <c r="K24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3977,13 +3986,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C25" s="52" t="n">
+      <c r="C25" s="53" t="n">
         <v>201775</v>
       </c>
-      <c r="D25" s="53" t="n">
+      <c r="D25" s="54" t="n">
         <v>32</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="54">
         <f>D25-D24</f>
         <v/>
       </c>
@@ -4007,58 +4016,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="54" t="n">
+      <c r="K25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4068,13 +4077,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C26" s="52" t="n">
+      <c r="C26" s="53" t="n">
         <v>256200</v>
       </c>
-      <c r="D26" s="53" t="n">
+      <c r="D26" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="54">
         <f>D26-D25</f>
         <v/>
       </c>
@@ -4098,58 +4107,58 @@
           <t>agi</t>
         </is>
       </c>
-      <c r="K26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="54" t="n">
+      <c r="K26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4159,13 +4168,13 @@
           <t>FED|3</t>
         </is>
       </c>
-      <c r="C27" s="52" t="n">
+      <c r="C27" s="53" t="n">
         <v>640600</v>
       </c>
-      <c r="D27" s="53" t="n">
+      <c r="D27" s="54" t="n">
         <v>37</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="54">
         <f>D27-D26</f>
         <v/>
       </c>
@@ -4176,13 +4185,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C28" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="53" t="n">
+      <c r="C28" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="54">
         <f>D28</f>
         <v/>
       </c>
@@ -4198,13 +4207,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C29" s="52" t="n">
+      <c r="C29" s="53" t="n">
         <v>12400</v>
       </c>
-      <c r="D29" s="53" t="n">
+      <c r="D29" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E29" s="53">
+      <c r="E29" s="54">
         <f>D29-D28</f>
         <v/>
       </c>
@@ -4215,13 +4224,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C30" s="52" t="n">
+      <c r="C30" s="53" t="n">
         <v>50400</v>
       </c>
-      <c r="D30" s="53" t="n">
+      <c r="D30" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="54">
         <f>D30-D29</f>
         <v/>
       </c>
@@ -4232,13 +4241,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C31" s="52" t="n">
+      <c r="C31" s="53" t="n">
         <v>105700</v>
       </c>
-      <c r="D31" s="53" t="n">
+      <c r="D31" s="54" t="n">
         <v>24</v>
       </c>
-      <c r="E31" s="53">
+      <c r="E31" s="54">
         <f>D31-D30</f>
         <v/>
       </c>
@@ -4249,13 +4258,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C32" s="52" t="n">
+      <c r="C32" s="53" t="n">
         <v>201775</v>
       </c>
-      <c r="D32" s="53" t="n">
+      <c r="D32" s="54" t="n">
         <v>32</v>
       </c>
-      <c r="E32" s="53">
+      <c r="E32" s="54">
         <f>D32-D31</f>
         <v/>
       </c>
@@ -4266,13 +4275,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C33" s="52" t="n">
+      <c r="C33" s="53" t="n">
         <v>256225</v>
       </c>
-      <c r="D33" s="53" t="n">
+      <c r="D33" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="E33" s="53">
+      <c r="E33" s="54">
         <f>D33-D32</f>
         <v/>
       </c>
@@ -4283,13 +4292,13 @@
           <t>FED|4</t>
         </is>
       </c>
-      <c r="C34" s="52" t="n">
+      <c r="C34" s="53" t="n">
         <v>384350</v>
       </c>
-      <c r="D34" s="53" t="n">
+      <c r="D34" s="54" t="n">
         <v>37</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E34" s="54">
         <f>D34-D33</f>
         <v/>
       </c>
@@ -4300,13 +4309,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C35" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="53" t="n">
+      <c r="C35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="53">
+      <c r="E35" s="54">
         <f>D35</f>
         <v/>
       </c>
@@ -4317,13 +4326,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C36" s="52" t="n">
+      <c r="C36" s="53" t="n">
         <v>11456</v>
       </c>
-      <c r="D36" s="53" t="n">
+      <c r="D36" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="54">
         <f>D36-D35</f>
         <v/>
       </c>
@@ -4334,13 +4343,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C37" s="52" t="n">
+      <c r="C37" s="53" t="n">
         <v>27157</v>
       </c>
-      <c r="D37" s="53" t="n">
+      <c r="D37" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="53">
+      <c r="E37" s="54">
         <f>D37-D36</f>
         <v/>
       </c>
@@ -4351,13 +4360,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C38" s="52" t="n">
+      <c r="C38" s="53" t="n">
         <v>42861</v>
       </c>
-      <c r="D38" s="53" t="n">
+      <c r="D38" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E38" s="53">
+      <c r="E38" s="54">
         <f>D38-D37</f>
         <v/>
       </c>
@@ -4368,13 +4377,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C39" s="52" t="n">
+      <c r="C39" s="53" t="n">
         <v>59498</v>
       </c>
-      <c r="D39" s="53" t="n">
+      <c r="D39" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="E39" s="53">
+      <c r="E39" s="54">
         <f>D39-D38</f>
         <v/>
       </c>
@@ -4385,13 +4394,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C40" s="52" t="n">
+      <c r="C40" s="53" t="n">
         <v>75197</v>
       </c>
-      <c r="D40" s="53" t="n">
+      <c r="D40" s="54" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E40" s="53">
+      <c r="E40" s="54">
         <f>D40-D39</f>
         <v/>
       </c>
@@ -4402,13 +4411,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C41" s="52" t="n">
+      <c r="C41" s="53" t="n">
         <v>384109</v>
       </c>
-      <c r="D41" s="53" t="n">
+      <c r="D41" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E41" s="53">
+      <c r="E41" s="54">
         <f>D41-D40</f>
         <v/>
       </c>
@@ -4419,13 +4428,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C42" s="52" t="n">
+      <c r="C42" s="53" t="n">
         <v>460927</v>
       </c>
-      <c r="D42" s="53" t="n">
+      <c r="D42" s="54" t="n">
         <v>11.3</v>
       </c>
-      <c r="E42" s="53">
+      <c r="E42" s="54">
         <f>D42-D41</f>
         <v/>
       </c>
@@ -4436,13 +4445,13 @@
           <t>CA|1</t>
         </is>
       </c>
-      <c r="C43" s="52" t="n">
+      <c r="C43" s="53" t="n">
         <v>768213</v>
       </c>
-      <c r="D43" s="53" t="n">
+      <c r="D43" s="54" t="n">
         <v>12.3</v>
       </c>
-      <c r="E43" s="53">
+      <c r="E43" s="54">
         <f>D43-D42</f>
         <v/>
       </c>
@@ -4453,13 +4462,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C44" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="53" t="n">
+      <c r="C44" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="53">
+      <c r="E44" s="54">
         <f>D44</f>
         <v/>
       </c>
@@ -4470,13 +4479,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C45" s="52" t="n">
+      <c r="C45" s="53" t="n">
         <v>22912</v>
       </c>
-      <c r="D45" s="53" t="n">
+      <c r="D45" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="53">
+      <c r="E45" s="54">
         <f>D45-D44</f>
         <v/>
       </c>
@@ -4487,13 +4496,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C46" s="52" t="n">
+      <c r="C46" s="53" t="n">
         <v>54314</v>
       </c>
-      <c r="D46" s="53" t="n">
+      <c r="D46" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="53">
+      <c r="E46" s="54">
         <f>D46-D45</f>
         <v/>
       </c>
@@ -4504,13 +4513,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C47" s="52" t="n">
+      <c r="C47" s="53" t="n">
         <v>85722</v>
       </c>
-      <c r="D47" s="53" t="n">
+      <c r="D47" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E47" s="53">
+      <c r="E47" s="54">
         <f>D47-D46</f>
         <v/>
       </c>
@@ -4521,13 +4530,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C48" s="52" t="n">
+      <c r="C48" s="53" t="n">
         <v>118996</v>
       </c>
-      <c r="D48" s="53" t="n">
+      <c r="D48" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="E48" s="53">
+      <c r="E48" s="54">
         <f>D48-D47</f>
         <v/>
       </c>
@@ -4538,13 +4547,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C49" s="52" t="n">
+      <c r="C49" s="53" t="n">
         <v>150394</v>
       </c>
-      <c r="D49" s="53" t="n">
+      <c r="D49" s="54" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E49" s="53">
+      <c r="E49" s="54">
         <f>D49-D48</f>
         <v/>
       </c>
@@ -4555,13 +4564,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C50" s="52" t="n">
+      <c r="C50" s="53" t="n">
         <v>768218</v>
       </c>
-      <c r="D50" s="53" t="n">
+      <c r="D50" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E50" s="53">
+      <c r="E50" s="54">
         <f>D50-D49</f>
         <v/>
       </c>
@@ -4572,13 +4581,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C51" s="52" t="n">
+      <c r="C51" s="53" t="n">
         <v>921854</v>
       </c>
-      <c r="D51" s="53" t="n">
+      <c r="D51" s="54" t="n">
         <v>11.3</v>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="54">
         <f>D51-D50</f>
         <v/>
       </c>
@@ -4589,13 +4598,13 @@
           <t>CA|2</t>
         </is>
       </c>
-      <c r="C52" s="52" t="n">
+      <c r="C52" s="53" t="n">
         <v>1536426</v>
       </c>
-      <c r="D52" s="53" t="n">
+      <c r="D52" s="54" t="n">
         <v>12.3</v>
       </c>
-      <c r="E52" s="53">
+      <c r="E52" s="54">
         <f>D52-D51</f>
         <v/>
       </c>
@@ -4606,13 +4615,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C53" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="53" t="n">
+      <c r="C53" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="53">
+      <c r="E53" s="54">
         <f>D53</f>
         <v/>
       </c>
@@ -4623,13 +4632,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C54" s="52" t="n">
+      <c r="C54" s="53" t="n">
         <v>22927</v>
       </c>
-      <c r="D54" s="53" t="n">
+      <c r="D54" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="53">
+      <c r="E54" s="54">
         <f>D54-D53</f>
         <v/>
       </c>
@@ -4640,13 +4649,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C55" s="52" t="n">
+      <c r="C55" s="53" t="n">
         <v>54316</v>
       </c>
-      <c r="D55" s="53" t="n">
+      <c r="D55" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E55" s="53">
+      <c r="E55" s="54">
         <f>D55-D54</f>
         <v/>
       </c>
@@ -4657,13 +4666,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C56" s="52" t="n">
+      <c r="C56" s="53" t="n">
         <v>70018</v>
       </c>
-      <c r="D56" s="53" t="n">
+      <c r="D56" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E56" s="53">
+      <c r="E56" s="54">
         <f>D56-D55</f>
         <v/>
       </c>
@@ -4674,13 +4683,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C57" s="52" t="n">
+      <c r="C57" s="53" t="n">
         <v>86654</v>
       </c>
-      <c r="D57" s="53" t="n">
+      <c r="D57" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="E57" s="53">
+      <c r="E57" s="54">
         <f>D57-D56</f>
         <v/>
       </c>
@@ -4691,13 +4700,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C58" s="52" t="n">
+      <c r="C58" s="53" t="n">
         <v>102356</v>
       </c>
-      <c r="D58" s="53" t="n">
+      <c r="D58" s="54" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E58" s="53">
+      <c r="E58" s="54">
         <f>D58-D57</f>
         <v/>
       </c>
@@ -4708,13 +4717,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C59" s="52" t="n">
+      <c r="C59" s="53" t="n">
         <v>522385</v>
       </c>
-      <c r="D59" s="53" t="n">
+      <c r="D59" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E59" s="53">
+      <c r="E59" s="54">
         <f>D59-D58</f>
         <v/>
       </c>
@@ -4725,13 +4734,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C60" s="52" t="n">
+      <c r="C60" s="53" t="n">
         <v>626864</v>
       </c>
-      <c r="D60" s="53" t="n">
+      <c r="D60" s="54" t="n">
         <v>11.3</v>
       </c>
-      <c r="E60" s="53">
+      <c r="E60" s="54">
         <f>D60-D59</f>
         <v/>
       </c>
@@ -4742,13 +4751,13 @@
           <t>CA|3</t>
         </is>
       </c>
-      <c r="C61" s="52" t="n">
+      <c r="C61" s="53" t="n">
         <v>1044771</v>
       </c>
-      <c r="D61" s="53" t="n">
+      <c r="D61" s="54" t="n">
         <v>12.3</v>
       </c>
-      <c r="E61" s="53">
+      <c r="E61" s="54">
         <f>D61-D60</f>
         <v/>
       </c>
@@ -4759,13 +4768,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C62" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="53" t="n">
+      <c r="C62" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="53">
+      <c r="E62" s="54">
         <f>D62</f>
         <v/>
       </c>
@@ -4776,13 +4785,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C63" s="52" t="n">
+      <c r="C63" s="53" t="n">
         <v>11456</v>
       </c>
-      <c r="D63" s="53" t="n">
+      <c r="D63" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="53">
+      <c r="E63" s="54">
         <f>D63-D62</f>
         <v/>
       </c>
@@ -4793,13 +4802,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C64" s="52" t="n">
+      <c r="C64" s="53" t="n">
         <v>27157</v>
       </c>
-      <c r="D64" s="53" t="n">
+      <c r="D64" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E64" s="53">
+      <c r="E64" s="54">
         <f>D64-D63</f>
         <v/>
       </c>
@@ -4810,13 +4819,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C65" s="52" t="n">
+      <c r="C65" s="53" t="n">
         <v>42861</v>
       </c>
-      <c r="D65" s="53" t="n">
+      <c r="D65" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E65" s="53">
+      <c r="E65" s="54">
         <f>D65-D64</f>
         <v/>
       </c>
@@ -4827,13 +4836,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C66" s="52" t="n">
+      <c r="C66" s="53" t="n">
         <v>59498</v>
       </c>
-      <c r="D66" s="53" t="n">
+      <c r="D66" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="E66" s="53">
+      <c r="E66" s="54">
         <f>D66-D65</f>
         <v/>
       </c>
@@ -4844,13 +4853,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C67" s="52" t="n">
+      <c r="C67" s="53" t="n">
         <v>75197</v>
       </c>
-      <c r="D67" s="53" t="n">
+      <c r="D67" s="54" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E67" s="53">
+      <c r="E67" s="54">
         <f>D67-D66</f>
         <v/>
       </c>
@@ -4861,13 +4870,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C68" s="52" t="n">
+      <c r="C68" s="53" t="n">
         <v>384109</v>
       </c>
-      <c r="D68" s="53" t="n">
+      <c r="D68" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E68" s="53">
+      <c r="E68" s="54">
         <f>D68-D67</f>
         <v/>
       </c>
@@ -4878,13 +4887,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C69" s="52" t="n">
+      <c r="C69" s="53" t="n">
         <v>460927</v>
       </c>
-      <c r="D69" s="53" t="n">
+      <c r="D69" s="54" t="n">
         <v>11.3</v>
       </c>
-      <c r="E69" s="53">
+      <c r="E69" s="54">
         <f>D69-D68</f>
         <v/>
       </c>
@@ -4895,13 +4904,13 @@
           <t>CA|4</t>
         </is>
       </c>
-      <c r="C70" s="52" t="n">
+      <c r="C70" s="53" t="n">
         <v>768213</v>
       </c>
-      <c r="D70" s="53" t="n">
+      <c r="D70" s="54" t="n">
         <v>12.3</v>
       </c>
-      <c r="E70" s="53">
+      <c r="E70" s="54">
         <f>D70-D69</f>
         <v/>
       </c>
@@ -4912,13 +4921,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C71" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="53" t="n">
+      <c r="C71" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="54" t="n">
         <v>1.4</v>
       </c>
-      <c r="E71" s="53">
+      <c r="E71" s="54">
         <f>D71</f>
         <v/>
       </c>
@@ -4929,13 +4938,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C72" s="52" t="n">
+      <c r="C72" s="53" t="n">
         <v>20000</v>
       </c>
-      <c r="D72" s="53" t="n">
+      <c r="D72" s="54" t="n">
         <v>1.75</v>
       </c>
-      <c r="E72" s="53">
+      <c r="E72" s="54">
         <f>D72-D71</f>
         <v/>
       </c>
@@ -4946,13 +4955,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C73" s="52" t="n">
+      <c r="C73" s="53" t="n">
         <v>35000</v>
       </c>
-      <c r="D73" s="53" t="n">
+      <c r="D73" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="E73" s="53">
+      <c r="E73" s="54">
         <f>D73-D72</f>
         <v/>
       </c>
@@ -4963,13 +4972,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C74" s="52" t="n">
+      <c r="C74" s="53" t="n">
         <v>40000</v>
       </c>
-      <c r="D74" s="53" t="n">
+      <c r="D74" s="54" t="n">
         <v>5.525</v>
       </c>
-      <c r="E74" s="53">
+      <c r="E74" s="54">
         <f>D74-D73</f>
         <v/>
       </c>
@@ -4980,13 +4989,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C75" s="52" t="n">
+      <c r="C75" s="53" t="n">
         <v>75000</v>
       </c>
-      <c r="D75" s="53" t="n">
+      <c r="D75" s="54" t="n">
         <v>6.37</v>
       </c>
-      <c r="E75" s="53">
+      <c r="E75" s="54">
         <f>D75-D74</f>
         <v/>
       </c>
@@ -4997,13 +5006,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C76" s="52" t="n">
+      <c r="C76" s="53" t="n">
         <v>500000</v>
       </c>
-      <c r="D76" s="53" t="n">
+      <c r="D76" s="54" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="E76" s="53">
+      <c r="E76" s="54">
         <f>D76-D75</f>
         <v/>
       </c>
@@ -5014,13 +5023,13 @@
           <t>NJ|1</t>
         </is>
       </c>
-      <c r="C77" s="52" t="n">
+      <c r="C77" s="53" t="n">
         <v>1000000</v>
       </c>
-      <c r="D77" s="53" t="n">
+      <c r="D77" s="54" t="n">
         <v>10.75</v>
       </c>
-      <c r="E77" s="53">
+      <c r="E77" s="54">
         <f>D77-D76</f>
         <v/>
       </c>
@@ -5031,13 +5040,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C78" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="53" t="n">
+      <c r="C78" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="54" t="n">
         <v>1.4</v>
       </c>
-      <c r="E78" s="53">
+      <c r="E78" s="54">
         <f>D78</f>
         <v/>
       </c>
@@ -5048,13 +5057,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C79" s="52" t="n">
+      <c r="C79" s="53" t="n">
         <v>20000</v>
       </c>
-      <c r="D79" s="53" t="n">
+      <c r="D79" s="54" t="n">
         <v>1.75</v>
       </c>
-      <c r="E79" s="53">
+      <c r="E79" s="54">
         <f>D79-D78</f>
         <v/>
       </c>
@@ -5065,13 +5074,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C80" s="52" t="n">
+      <c r="C80" s="53" t="n">
         <v>50000</v>
       </c>
-      <c r="D80" s="53" t="n">
+      <c r="D80" s="54" t="n">
         <v>2.45</v>
       </c>
-      <c r="E80" s="53">
+      <c r="E80" s="54">
         <f>D80-D79</f>
         <v/>
       </c>
@@ -5082,13 +5091,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C81" s="52" t="n">
+      <c r="C81" s="53" t="n">
         <v>70000</v>
       </c>
-      <c r="D81" s="53" t="n">
+      <c r="D81" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="E81" s="53">
+      <c r="E81" s="54">
         <f>D81-D80</f>
         <v/>
       </c>
@@ -5099,13 +5108,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C82" s="52" t="n">
+      <c r="C82" s="53" t="n">
         <v>80000</v>
       </c>
-      <c r="D82" s="53" t="n">
+      <c r="D82" s="54" t="n">
         <v>5.525</v>
       </c>
-      <c r="E82" s="53">
+      <c r="E82" s="54">
         <f>D82-D81</f>
         <v/>
       </c>
@@ -5116,13 +5125,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C83" s="52" t="n">
+      <c r="C83" s="53" t="n">
         <v>150000</v>
       </c>
-      <c r="D83" s="53" t="n">
+      <c r="D83" s="54" t="n">
         <v>6.37</v>
       </c>
-      <c r="E83" s="53">
+      <c r="E83" s="54">
         <f>D83-D82</f>
         <v/>
       </c>
@@ -5133,13 +5142,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C84" s="52" t="n">
+      <c r="C84" s="53" t="n">
         <v>500000</v>
       </c>
-      <c r="D84" s="53" t="n">
+      <c r="D84" s="54" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="E84" s="53">
+      <c r="E84" s="54">
         <f>D84-D83</f>
         <v/>
       </c>
@@ -5150,13 +5159,13 @@
           <t>NJ|2</t>
         </is>
       </c>
-      <c r="C85" s="52" t="n">
+      <c r="C85" s="53" t="n">
         <v>1000000</v>
       </c>
-      <c r="D85" s="53" t="n">
+      <c r="D85" s="54" t="n">
         <v>10.75</v>
       </c>
-      <c r="E85" s="53">
+      <c r="E85" s="54">
         <f>D85-D84</f>
         <v/>
       </c>
@@ -5167,13 +5176,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C86" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="53" t="n">
+      <c r="C86" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="54" t="n">
         <v>1.4</v>
       </c>
-      <c r="E86" s="53">
+      <c r="E86" s="54">
         <f>D86</f>
         <v/>
       </c>
@@ -5184,13 +5193,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C87" s="52" t="n">
+      <c r="C87" s="53" t="n">
         <v>20000</v>
       </c>
-      <c r="D87" s="53" t="n">
+      <c r="D87" s="54" t="n">
         <v>1.75</v>
       </c>
-      <c r="E87" s="53">
+      <c r="E87" s="54">
         <f>D87-D86</f>
         <v/>
       </c>
@@ -5201,13 +5210,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C88" s="52" t="n">
+      <c r="C88" s="53" t="n">
         <v>50000</v>
       </c>
-      <c r="D88" s="53" t="n">
+      <c r="D88" s="54" t="n">
         <v>2.45</v>
       </c>
-      <c r="E88" s="53">
+      <c r="E88" s="54">
         <f>D88-D87</f>
         <v/>
       </c>
@@ -5218,13 +5227,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C89" s="52" t="n">
+      <c r="C89" s="53" t="n">
         <v>70000</v>
       </c>
-      <c r="D89" s="53" t="n">
+      <c r="D89" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="E89" s="53">
+      <c r="E89" s="54">
         <f>D89-D88</f>
         <v/>
       </c>
@@ -5235,13 +5244,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C90" s="52" t="n">
+      <c r="C90" s="53" t="n">
         <v>80000</v>
       </c>
-      <c r="D90" s="53" t="n">
+      <c r="D90" s="54" t="n">
         <v>5.525</v>
       </c>
-      <c r="E90" s="53">
+      <c r="E90" s="54">
         <f>D90-D89</f>
         <v/>
       </c>
@@ -5252,13 +5261,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C91" s="52" t="n">
+      <c r="C91" s="53" t="n">
         <v>150000</v>
       </c>
-      <c r="D91" s="53" t="n">
+      <c r="D91" s="54" t="n">
         <v>6.37</v>
       </c>
-      <c r="E91" s="53">
+      <c r="E91" s="54">
         <f>D91-D90</f>
         <v/>
       </c>
@@ -5269,13 +5278,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C92" s="52" t="n">
+      <c r="C92" s="53" t="n">
         <v>500000</v>
       </c>
-      <c r="D92" s="53" t="n">
+      <c r="D92" s="54" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="E92" s="53">
+      <c r="E92" s="54">
         <f>D92-D91</f>
         <v/>
       </c>
@@ -5286,13 +5295,13 @@
           <t>NJ|3</t>
         </is>
       </c>
-      <c r="C93" s="52" t="n">
+      <c r="C93" s="53" t="n">
         <v>1000000</v>
       </c>
-      <c r="D93" s="53" t="n">
+      <c r="D93" s="54" t="n">
         <v>10.75</v>
       </c>
-      <c r="E93" s="53">
+      <c r="E93" s="54">
         <f>D93-D92</f>
         <v/>
       </c>
@@ -5303,13 +5312,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C94" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="53" t="n">
+      <c r="C94" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="54" t="n">
         <v>1.4</v>
       </c>
-      <c r="E94" s="53">
+      <c r="E94" s="54">
         <f>D94</f>
         <v/>
       </c>
@@ -5320,13 +5329,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C95" s="52" t="n">
+      <c r="C95" s="53" t="n">
         <v>20000</v>
       </c>
-      <c r="D95" s="53" t="n">
+      <c r="D95" s="54" t="n">
         <v>1.75</v>
       </c>
-      <c r="E95" s="53">
+      <c r="E95" s="54">
         <f>D95-D94</f>
         <v/>
       </c>
@@ -5337,13 +5346,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C96" s="52" t="n">
+      <c r="C96" s="53" t="n">
         <v>35000</v>
       </c>
-      <c r="D96" s="53" t="n">
+      <c r="D96" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="E96" s="53">
+      <c r="E96" s="54">
         <f>D96-D95</f>
         <v/>
       </c>
@@ -5354,13 +5363,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C97" s="52" t="n">
+      <c r="C97" s="53" t="n">
         <v>40000</v>
       </c>
-      <c r="D97" s="53" t="n">
+      <c r="D97" s="54" t="n">
         <v>5.525</v>
       </c>
-      <c r="E97" s="53">
+      <c r="E97" s="54">
         <f>D97-D96</f>
         <v/>
       </c>
@@ -5371,13 +5380,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C98" s="52" t="n">
+      <c r="C98" s="53" t="n">
         <v>75000</v>
       </c>
-      <c r="D98" s="53" t="n">
+      <c r="D98" s="54" t="n">
         <v>6.37</v>
       </c>
-      <c r="E98" s="53">
+      <c r="E98" s="54">
         <f>D98-D97</f>
         <v/>
       </c>
@@ -5388,13 +5397,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C99" s="52" t="n">
+      <c r="C99" s="53" t="n">
         <v>500000</v>
       </c>
-      <c r="D99" s="53" t="n">
+      <c r="D99" s="54" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="E99" s="53">
+      <c r="E99" s="54">
         <f>D99-D98</f>
         <v/>
       </c>
@@ -5405,13 +5414,13 @@
           <t>NJ|4</t>
         </is>
       </c>
-      <c r="C100" s="52" t="n">
+      <c r="C100" s="53" t="n">
         <v>1000000</v>
       </c>
-      <c r="D100" s="53" t="n">
+      <c r="D100" s="54" t="n">
         <v>10.75</v>
       </c>
-      <c r="E100" s="53">
+      <c r="E100" s="54">
         <f>D100-D99</f>
         <v/>
       </c>
@@ -5422,13 +5431,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C101" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="53" t="n">
+      <c r="C101" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="54" t="n">
         <v>3.9</v>
       </c>
-      <c r="E101" s="53">
+      <c r="E101" s="54">
         <f>D101</f>
         <v/>
       </c>
@@ -5439,13 +5448,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C102" s="52" t="n">
+      <c r="C102" s="53" t="n">
         <v>8500</v>
       </c>
-      <c r="D102" s="53" t="n">
+      <c r="D102" s="54" t="n">
         <v>4.4</v>
       </c>
-      <c r="E102" s="53">
+      <c r="E102" s="54">
         <f>D102-D101</f>
         <v/>
       </c>
@@ -5456,13 +5465,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C103" s="52" t="n">
+      <c r="C103" s="53" t="n">
         <v>11700</v>
       </c>
-      <c r="D103" s="53" t="n">
+      <c r="D103" s="54" t="n">
         <v>5.15</v>
       </c>
-      <c r="E103" s="53">
+      <c r="E103" s="54">
         <f>D103-D102</f>
         <v/>
       </c>
@@ -5473,13 +5482,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C104" s="52" t="n">
+      <c r="C104" s="53" t="n">
         <v>13900</v>
       </c>
-      <c r="D104" s="53" t="n">
+      <c r="D104" s="54" t="n">
         <v>5.4</v>
       </c>
-      <c r="E104" s="53">
+      <c r="E104" s="54">
         <f>D104-D103</f>
         <v/>
       </c>
@@ -5490,13 +5499,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C105" s="52" t="n">
+      <c r="C105" s="53" t="n">
         <v>80650</v>
       </c>
-      <c r="D105" s="53" t="n">
+      <c r="D105" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E105" s="53">
+      <c r="E105" s="54">
         <f>D105-D104</f>
         <v/>
       </c>
@@ -5507,13 +5516,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C106" s="52" t="n">
+      <c r="C106" s="53" t="n">
         <v>215400</v>
       </c>
-      <c r="D106" s="53" t="n">
+      <c r="D106" s="54" t="n">
         <v>6.85</v>
       </c>
-      <c r="E106" s="53">
+      <c r="E106" s="54">
         <f>D106-D105</f>
         <v/>
       </c>
@@ -5524,13 +5533,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C107" s="52" t="n">
+      <c r="C107" s="53" t="n">
         <v>1077550</v>
       </c>
-      <c r="D107" s="53" t="n">
+      <c r="D107" s="54" t="n">
         <v>9.65</v>
       </c>
-      <c r="E107" s="53">
+      <c r="E107" s="54">
         <f>D107-D106</f>
         <v/>
       </c>
@@ -5541,13 +5550,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C108" s="52" t="n">
+      <c r="C108" s="53" t="n">
         <v>5000000</v>
       </c>
-      <c r="D108" s="53" t="n">
+      <c r="D108" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E108" s="53">
+      <c r="E108" s="54">
         <f>D108-D107</f>
         <v/>
       </c>
@@ -5558,13 +5567,13 @@
           <t>NY|1</t>
         </is>
       </c>
-      <c r="C109" s="52" t="n">
+      <c r="C109" s="53" t="n">
         <v>25000000</v>
       </c>
-      <c r="D109" s="53" t="n">
+      <c r="D109" s="54" t="n">
         <v>10.9</v>
       </c>
-      <c r="E109" s="53">
+      <c r="E109" s="54">
         <f>D109-D108</f>
         <v/>
       </c>
@@ -5575,13 +5584,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C110" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="53" t="n">
+      <c r="C110" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="54" t="n">
         <v>3.9</v>
       </c>
-      <c r="E110" s="53">
+      <c r="E110" s="54">
         <f>D110</f>
         <v/>
       </c>
@@ -5592,13 +5601,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C111" s="52" t="n">
+      <c r="C111" s="53" t="n">
         <v>17150</v>
       </c>
-      <c r="D111" s="53" t="n">
+      <c r="D111" s="54" t="n">
         <v>4.4</v>
       </c>
-      <c r="E111" s="53">
+      <c r="E111" s="54">
         <f>D111-D110</f>
         <v/>
       </c>
@@ -5609,13 +5618,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C112" s="52" t="n">
+      <c r="C112" s="53" t="n">
         <v>23600</v>
       </c>
-      <c r="D112" s="53" t="n">
+      <c r="D112" s="54" t="n">
         <v>5.15</v>
       </c>
-      <c r="E112" s="53">
+      <c r="E112" s="54">
         <f>D112-D111</f>
         <v/>
       </c>
@@ -5626,13 +5635,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C113" s="52" t="n">
+      <c r="C113" s="53" t="n">
         <v>27900</v>
       </c>
-      <c r="D113" s="53" t="n">
+      <c r="D113" s="54" t="n">
         <v>5.4</v>
       </c>
-      <c r="E113" s="53">
+      <c r="E113" s="54">
         <f>D113-D112</f>
         <v/>
       </c>
@@ -5643,13 +5652,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C114" s="52" t="n">
+      <c r="C114" s="53" t="n">
         <v>161550</v>
       </c>
-      <c r="D114" s="53" t="n">
+      <c r="D114" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E114" s="53">
+      <c r="E114" s="54">
         <f>D114-D113</f>
         <v/>
       </c>
@@ -5660,13 +5669,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C115" s="52" t="n">
+      <c r="C115" s="53" t="n">
         <v>323200</v>
       </c>
-      <c r="D115" s="53" t="n">
+      <c r="D115" s="54" t="n">
         <v>6.85</v>
       </c>
-      <c r="E115" s="53">
+      <c r="E115" s="54">
         <f>D115-D114</f>
         <v/>
       </c>
@@ -5677,13 +5686,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C116" s="52" t="n">
+      <c r="C116" s="53" t="n">
         <v>2155350</v>
       </c>
-      <c r="D116" s="53" t="n">
+      <c r="D116" s="54" t="n">
         <v>9.65</v>
       </c>
-      <c r="E116" s="53">
+      <c r="E116" s="54">
         <f>D116-D115</f>
         <v/>
       </c>
@@ -5694,13 +5703,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C117" s="52" t="n">
+      <c r="C117" s="53" t="n">
         <v>5000000</v>
       </c>
-      <c r="D117" s="53" t="n">
+      <c r="D117" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E117" s="53">
+      <c r="E117" s="54">
         <f>D117-D116</f>
         <v/>
       </c>
@@ -5711,13 +5720,13 @@
           <t>NY|2</t>
         </is>
       </c>
-      <c r="C118" s="52" t="n">
+      <c r="C118" s="53" t="n">
         <v>25000000</v>
       </c>
-      <c r="D118" s="53" t="n">
+      <c r="D118" s="54" t="n">
         <v>10.9</v>
       </c>
-      <c r="E118" s="53">
+      <c r="E118" s="54">
         <f>D118-D117</f>
         <v/>
       </c>
@@ -5728,13 +5737,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C119" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="53" t="n">
+      <c r="C119" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="54" t="n">
         <v>3.9</v>
       </c>
-      <c r="E119" s="53">
+      <c r="E119" s="54">
         <f>D119</f>
         <v/>
       </c>
@@ -5745,13 +5754,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C120" s="52" t="n">
+      <c r="C120" s="53" t="n">
         <v>12800</v>
       </c>
-      <c r="D120" s="53" t="n">
+      <c r="D120" s="54" t="n">
         <v>4.4</v>
       </c>
-      <c r="E120" s="53">
+      <c r="E120" s="54">
         <f>D120-D119</f>
         <v/>
       </c>
@@ -5762,13 +5771,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C121" s="52" t="n">
+      <c r="C121" s="53" t="n">
         <v>17650</v>
       </c>
-      <c r="D121" s="53" t="n">
+      <c r="D121" s="54" t="n">
         <v>5.15</v>
       </c>
-      <c r="E121" s="53">
+      <c r="E121" s="54">
         <f>D121-D120</f>
         <v/>
       </c>
@@ -5779,13 +5788,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C122" s="52" t="n">
+      <c r="C122" s="53" t="n">
         <v>20900</v>
       </c>
-      <c r="D122" s="53" t="n">
+      <c r="D122" s="54" t="n">
         <v>5.4</v>
       </c>
-      <c r="E122" s="53">
+      <c r="E122" s="54">
         <f>D122-D121</f>
         <v/>
       </c>
@@ -5796,13 +5805,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C123" s="52" t="n">
+      <c r="C123" s="53" t="n">
         <v>107650</v>
       </c>
-      <c r="D123" s="53" t="n">
+      <c r="D123" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E123" s="53">
+      <c r="E123" s="54">
         <f>D123-D122</f>
         <v/>
       </c>
@@ -5813,13 +5822,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C124" s="52" t="n">
+      <c r="C124" s="53" t="n">
         <v>269300</v>
       </c>
-      <c r="D124" s="53" t="n">
+      <c r="D124" s="54" t="n">
         <v>6.85</v>
       </c>
-      <c r="E124" s="53">
+      <c r="E124" s="54">
         <f>D124-D123</f>
         <v/>
       </c>
@@ -5830,13 +5839,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C125" s="52" t="n">
+      <c r="C125" s="53" t="n">
         <v>1616450</v>
       </c>
-      <c r="D125" s="53" t="n">
+      <c r="D125" s="54" t="n">
         <v>9.65</v>
       </c>
-      <c r="E125" s="53">
+      <c r="E125" s="54">
         <f>D125-D124</f>
         <v/>
       </c>
@@ -5847,13 +5856,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C126" s="52" t="n">
+      <c r="C126" s="53" t="n">
         <v>5000000</v>
       </c>
-      <c r="D126" s="53" t="n">
+      <c r="D126" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E126" s="53">
+      <c r="E126" s="54">
         <f>D126-D125</f>
         <v/>
       </c>
@@ -5864,13 +5873,13 @@
           <t>NY|3</t>
         </is>
       </c>
-      <c r="C127" s="52" t="n">
+      <c r="C127" s="53" t="n">
         <v>25000000</v>
       </c>
-      <c r="D127" s="53" t="n">
+      <c r="D127" s="54" t="n">
         <v>10.9</v>
       </c>
-      <c r="E127" s="53">
+      <c r="E127" s="54">
         <f>D127-D126</f>
         <v/>
       </c>
@@ -5881,13 +5890,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C128" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="53" t="n">
+      <c r="C128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="54" t="n">
         <v>3.9</v>
       </c>
-      <c r="E128" s="53">
+      <c r="E128" s="54">
         <f>D128</f>
         <v/>
       </c>
@@ -5898,13 +5907,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C129" s="52" t="n">
+      <c r="C129" s="53" t="n">
         <v>8500</v>
       </c>
-      <c r="D129" s="53" t="n">
+      <c r="D129" s="54" t="n">
         <v>4.4</v>
       </c>
-      <c r="E129" s="53">
+      <c r="E129" s="54">
         <f>D129-D128</f>
         <v/>
       </c>
@@ -5915,13 +5924,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C130" s="52" t="n">
+      <c r="C130" s="53" t="n">
         <v>11700</v>
       </c>
-      <c r="D130" s="53" t="n">
+      <c r="D130" s="54" t="n">
         <v>5.15</v>
       </c>
-      <c r="E130" s="53">
+      <c r="E130" s="54">
         <f>D130-D129</f>
         <v/>
       </c>
@@ -5932,13 +5941,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C131" s="52" t="n">
+      <c r="C131" s="53" t="n">
         <v>13900</v>
       </c>
-      <c r="D131" s="53" t="n">
+      <c r="D131" s="54" t="n">
         <v>5.4</v>
       </c>
-      <c r="E131" s="53">
+      <c r="E131" s="54">
         <f>D131-D130</f>
         <v/>
       </c>
@@ -5949,13 +5958,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C132" s="52" t="n">
+      <c r="C132" s="53" t="n">
         <v>80650</v>
       </c>
-      <c r="D132" s="53" t="n">
+      <c r="D132" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E132" s="53">
+      <c r="E132" s="54">
         <f>D132-D131</f>
         <v/>
       </c>
@@ -5966,13 +5975,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C133" s="52" t="n">
+      <c r="C133" s="53" t="n">
         <v>215400</v>
       </c>
-      <c r="D133" s="53" t="n">
+      <c r="D133" s="54" t="n">
         <v>6.85</v>
       </c>
-      <c r="E133" s="53">
+      <c r="E133" s="54">
         <f>D133-D132</f>
         <v/>
       </c>
@@ -5983,13 +5992,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C134" s="52" t="n">
+      <c r="C134" s="53" t="n">
         <v>1077550</v>
       </c>
-      <c r="D134" s="53" t="n">
+      <c r="D134" s="54" t="n">
         <v>9.65</v>
       </c>
-      <c r="E134" s="53">
+      <c r="E134" s="54">
         <f>D134-D133</f>
         <v/>
       </c>
@@ -6000,13 +6009,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C135" s="52" t="n">
+      <c r="C135" s="53" t="n">
         <v>5000000</v>
       </c>
-      <c r="D135" s="53" t="n">
+      <c r="D135" s="54" t="n">
         <v>10.3</v>
       </c>
-      <c r="E135" s="53">
+      <c r="E135" s="54">
         <f>D135-D134</f>
         <v/>
       </c>
@@ -6017,13 +6026,13 @@
           <t>NY|4</t>
         </is>
       </c>
-      <c r="C136" s="52" t="n">
+      <c r="C136" s="53" t="n">
         <v>25000000</v>
       </c>
-      <c r="D136" s="53" t="n">
+      <c r="D136" s="54" t="n">
         <v>10.9</v>
       </c>
-      <c r="E136" s="53">
+      <c r="E136" s="54">
         <f>D136-D135</f>
         <v/>
       </c>
@@ -6034,13 +6043,13 @@
           <t>NM|1</t>
         </is>
       </c>
-      <c r="C137" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="53" t="n">
+      <c r="C137" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E137" s="53">
+      <c r="E137" s="54">
         <f>D137</f>
         <v/>
       </c>
@@ -6051,13 +6060,13 @@
           <t>NM|1</t>
         </is>
       </c>
-      <c r="C138" s="52" t="n">
+      <c r="C138" s="53" t="n">
         <v>5500</v>
       </c>
-      <c r="D138" s="53" t="n">
+      <c r="D138" s="54" t="n">
         <v>3.2</v>
       </c>
-      <c r="E138" s="53">
+      <c r="E138" s="54">
         <f>D138-D137</f>
         <v/>
       </c>
@@ -6068,13 +6077,13 @@
           <t>NM|1</t>
         </is>
       </c>
-      <c r="C139" s="52" t="n">
+      <c r="C139" s="53" t="n">
         <v>16500</v>
       </c>
-      <c r="D139" s="53" t="n">
+      <c r="D139" s="54" t="n">
         <v>4.3</v>
       </c>
-      <c r="E139" s="53">
+      <c r="E139" s="54">
         <f>D139-D138</f>
         <v/>
       </c>
@@ -6085,13 +6094,13 @@
           <t>NM|1</t>
         </is>
       </c>
-      <c r="C140" s="52" t="n">
+      <c r="C140" s="53" t="n">
         <v>33500</v>
       </c>
-      <c r="D140" s="53" t="n">
+      <c r="D140" s="54" t="n">
         <v>4.7</v>
       </c>
-      <c r="E140" s="53">
+      <c r="E140" s="54">
         <f>D140-D139</f>
         <v/>
       </c>
@@ -6102,13 +6111,13 @@
           <t>NM|1</t>
         </is>
       </c>
-      <c r="C141" s="52" t="n">
+      <c r="C141" s="53" t="n">
         <v>66500</v>
       </c>
-      <c r="D141" s="53" t="n">
+      <c r="D141" s="54" t="n">
         <v>4.9</v>
       </c>
-      <c r="E141" s="53">
+      <c r="E141" s="54">
         <f>D141-D140</f>
         <v/>
       </c>
@@ -6119,13 +6128,13 @@
           <t>NM|1</t>
         </is>
       </c>
-      <c r="C142" s="52" t="n">
+      <c r="C142" s="53" t="n">
         <v>210000</v>
       </c>
-      <c r="D142" s="53" t="n">
+      <c r="D142" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E142" s="53">
+      <c r="E142" s="54">
         <f>D142-D141</f>
         <v/>
       </c>
@@ -6136,13 +6145,13 @@
           <t>NM|2</t>
         </is>
       </c>
-      <c r="C143" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="53" t="n">
+      <c r="C143" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E143" s="53">
+      <c r="E143" s="54">
         <f>D143</f>
         <v/>
       </c>
@@ -6153,13 +6162,13 @@
           <t>NM|2</t>
         </is>
       </c>
-      <c r="C144" s="52" t="n">
+      <c r="C144" s="53" t="n">
         <v>8000</v>
       </c>
-      <c r="D144" s="53" t="n">
+      <c r="D144" s="54" t="n">
         <v>3.2</v>
       </c>
-      <c r="E144" s="53">
+      <c r="E144" s="54">
         <f>D144-D143</f>
         <v/>
       </c>
@@ -6170,13 +6179,13 @@
           <t>NM|2</t>
         </is>
       </c>
-      <c r="C145" s="52" t="n">
+      <c r="C145" s="53" t="n">
         <v>25000</v>
       </c>
-      <c r="D145" s="53" t="n">
+      <c r="D145" s="54" t="n">
         <v>4.3</v>
       </c>
-      <c r="E145" s="53">
+      <c r="E145" s="54">
         <f>D145-D144</f>
         <v/>
       </c>
@@ -6187,13 +6196,13 @@
           <t>NM|2</t>
         </is>
       </c>
-      <c r="C146" s="52" t="n">
+      <c r="C146" s="53" t="n">
         <v>50000</v>
       </c>
-      <c r="D146" s="53" t="n">
+      <c r="D146" s="54" t="n">
         <v>4.7</v>
       </c>
-      <c r="E146" s="53">
+      <c r="E146" s="54">
         <f>D146-D145</f>
         <v/>
       </c>
@@ -6204,13 +6213,13 @@
           <t>NM|2</t>
         </is>
       </c>
-      <c r="C147" s="52" t="n">
+      <c r="C147" s="53" t="n">
         <v>100000</v>
       </c>
-      <c r="D147" s="53" t="n">
+      <c r="D147" s="54" t="n">
         <v>4.9</v>
       </c>
-      <c r="E147" s="53">
+      <c r="E147" s="54">
         <f>D147-D146</f>
         <v/>
       </c>
@@ -6221,13 +6230,13 @@
           <t>NM|2</t>
         </is>
       </c>
-      <c r="C148" s="52" t="n">
+      <c r="C148" s="53" t="n">
         <v>315000</v>
       </c>
-      <c r="D148" s="53" t="n">
+      <c r="D148" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E148" s="53">
+      <c r="E148" s="54">
         <f>D148-D147</f>
         <v/>
       </c>
@@ -6238,13 +6247,13 @@
           <t>NM|3</t>
         </is>
       </c>
-      <c r="C149" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="53" t="n">
+      <c r="C149" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E149" s="53">
+      <c r="E149" s="54">
         <f>D149</f>
         <v/>
       </c>
@@ -6255,13 +6264,13 @@
           <t>NM|3</t>
         </is>
       </c>
-      <c r="C150" s="52" t="n">
+      <c r="C150" s="53" t="n">
         <v>8000</v>
       </c>
-      <c r="D150" s="53" t="n">
+      <c r="D150" s="54" t="n">
         <v>3.2</v>
       </c>
-      <c r="E150" s="53">
+      <c r="E150" s="54">
         <f>D150-D149</f>
         <v/>
       </c>
@@ -6272,13 +6281,13 @@
           <t>NM|3</t>
         </is>
       </c>
-      <c r="C151" s="52" t="n">
+      <c r="C151" s="53" t="n">
         <v>25000</v>
       </c>
-      <c r="D151" s="53" t="n">
+      <c r="D151" s="54" t="n">
         <v>4.3</v>
       </c>
-      <c r="E151" s="53">
+      <c r="E151" s="54">
         <f>D151-D150</f>
         <v/>
       </c>
@@ -6289,13 +6298,13 @@
           <t>NM|3</t>
         </is>
       </c>
-      <c r="C152" s="52" t="n">
+      <c r="C152" s="53" t="n">
         <v>50000</v>
       </c>
-      <c r="D152" s="53" t="n">
+      <c r="D152" s="54" t="n">
         <v>4.7</v>
       </c>
-      <c r="E152" s="53">
+      <c r="E152" s="54">
         <f>D152-D151</f>
         <v/>
       </c>
@@ -6306,13 +6315,13 @@
           <t>NM|3</t>
         </is>
       </c>
-      <c r="C153" s="52" t="n">
+      <c r="C153" s="53" t="n">
         <v>100000</v>
       </c>
-      <c r="D153" s="53" t="n">
+      <c r="D153" s="54" t="n">
         <v>4.9</v>
       </c>
-      <c r="E153" s="53">
+      <c r="E153" s="54">
         <f>D153-D152</f>
         <v/>
       </c>
@@ -6323,13 +6332,13 @@
           <t>NM|3</t>
         </is>
       </c>
-      <c r="C154" s="52" t="n">
+      <c r="C154" s="53" t="n">
         <v>315000</v>
       </c>
-      <c r="D154" s="53" t="n">
+      <c r="D154" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E154" s="53">
+      <c r="E154" s="54">
         <f>D154-D153</f>
         <v/>
       </c>
@@ -6340,13 +6349,13 @@
           <t>NM|4</t>
         </is>
       </c>
-      <c r="C155" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="53" t="n">
+      <c r="C155" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E155" s="53">
+      <c r="E155" s="54">
         <f>D155</f>
         <v/>
       </c>
@@ -6357,13 +6366,13 @@
           <t>NM|4</t>
         </is>
       </c>
-      <c r="C156" s="52" t="n">
+      <c r="C156" s="53" t="n">
         <v>4000</v>
       </c>
-      <c r="D156" s="53" t="n">
+      <c r="D156" s="54" t="n">
         <v>3.2</v>
       </c>
-      <c r="E156" s="53">
+      <c r="E156" s="54">
         <f>D156-D155</f>
         <v/>
       </c>
@@ -6374,13 +6383,13 @@
           <t>NM|4</t>
         </is>
       </c>
-      <c r="C157" s="52" t="n">
+      <c r="C157" s="53" t="n">
         <v>12500</v>
       </c>
-      <c r="D157" s="53" t="n">
+      <c r="D157" s="54" t="n">
         <v>4.3</v>
       </c>
-      <c r="E157" s="53">
+      <c r="E157" s="54">
         <f>D157-D156</f>
         <v/>
       </c>
@@ -6391,13 +6400,13 @@
           <t>NM|4</t>
         </is>
       </c>
-      <c r="C158" s="52" t="n">
+      <c r="C158" s="53" t="n">
         <v>25000</v>
       </c>
-      <c r="D158" s="53" t="n">
+      <c r="D158" s="54" t="n">
         <v>4.7</v>
       </c>
-      <c r="E158" s="53">
+      <c r="E158" s="54">
         <f>D158-D157</f>
         <v/>
       </c>
@@ -6408,13 +6417,13 @@
           <t>NM|4</t>
         </is>
       </c>
-      <c r="C159" s="52" t="n">
+      <c r="C159" s="53" t="n">
         <v>50000</v>
       </c>
-      <c r="D159" s="53" t="n">
+      <c r="D159" s="54" t="n">
         <v>4.9</v>
       </c>
-      <c r="E159" s="53">
+      <c r="E159" s="54">
         <f>D159-D158</f>
         <v/>
       </c>
@@ -6425,13 +6434,13 @@
           <t>NM|4</t>
         </is>
       </c>
-      <c r="C160" s="52" t="n">
+      <c r="C160" s="53" t="n">
         <v>157500</v>
       </c>
-      <c r="D160" s="53" t="n">
+      <c r="D160" s="54" t="n">
         <v>5.9</v>
       </c>
-      <c r="E160" s="53">
+      <c r="E160" s="54">
         <f>D160-D159</f>
         <v/>
       </c>
@@ -6969,15 +6978,10 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Escribe tú en las celdas amarillas. Las demás se calculan solas: no hace falta tocarlas.</t>
+          <t>✎  Las celdas amarillas las rellenas tú; el resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -7938,15 +7942,10 @@
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Escribe tú en las celdas amarillas. Las demás se calculan solas: no hace falta tocarlas.</t>
+          <t>✎  Las celdas amarillas las rellenas tú; el resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8467,7 @@
           <t>SSA / IRS</t>
         </is>
       </c>
-      <c r="E8" s="30" t="n"/>
+      <c r="E8" s="48" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="45" t="inlineStr">
@@ -8486,7 +8485,7 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="E9" s="30" t="n"/>
+      <c r="E9" s="48" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="45" t="inlineStr">
@@ -8504,7 +8503,7 @@
           <t>Tu banco</t>
         </is>
       </c>
-      <c r="E10" s="30" t="n"/>
+      <c r="E10" s="48" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="17" t="inlineStr">
@@ -8532,7 +8531,7 @@
           <t>Cada empleador</t>
         </is>
       </c>
-      <c r="E12" s="30" t="n"/>
+      <c r="E12" s="48" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="45" t="inlineStr">
@@ -8550,7 +8549,7 @@
           <t>Cada cliente</t>
         </is>
       </c>
-      <c r="E13" s="30" t="n"/>
+      <c r="E13" s="48" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="45" t="inlineStr">
@@ -8568,7 +8567,7 @@
           <t>La plataforma</t>
         </is>
       </c>
-      <c r="E14" s="30" t="n"/>
+      <c r="E14" s="48" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="45" t="inlineStr">
@@ -8586,7 +8585,7 @@
           <t>Banco o bróker</t>
         </is>
       </c>
-      <c r="E15" s="30" t="n"/>
+      <c r="E15" s="48" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="45" t="inlineStr">
@@ -8604,7 +8603,7 @@
           <t>Tu estado</t>
         </is>
       </c>
-      <c r="E16" s="30" t="n"/>
+      <c r="E16" s="48" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="45" t="inlineStr">
@@ -8622,7 +8621,7 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="E17" s="30" t="n"/>
+      <c r="E17" s="48" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="17" t="inlineStr">
@@ -8650,7 +8649,7 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="E19" s="30" t="n"/>
+      <c r="E19" s="48" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="45" t="inlineStr">
@@ -8668,7 +8667,7 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="E20" s="30" t="n"/>
+      <c r="E20" s="48" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="45" t="inlineStr">
@@ -8686,7 +8685,7 @@
           <t>Tú / IRS</t>
         </is>
       </c>
-      <c r="E21" s="30" t="n"/>
+      <c r="E21" s="48" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="17" t="inlineStr">
@@ -8714,7 +8713,7 @@
           <t>Tu banco</t>
         </is>
       </c>
-      <c r="E23" s="30" t="n"/>
+      <c r="E23" s="48" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="45" t="inlineStr">
@@ -8732,7 +8731,7 @@
           <t>Quien te prestó</t>
         </is>
       </c>
-      <c r="E24" s="30" t="n"/>
+      <c r="E24" s="48" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="45" t="inlineStr">
@@ -8750,7 +8749,7 @@
           <t>La universidad</t>
         </is>
       </c>
-      <c r="E25" s="30" t="n"/>
+      <c r="E25" s="48" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="45" t="inlineStr">
@@ -8768,7 +8767,7 @@
           <t>HealthCare.gov</t>
         </is>
       </c>
-      <c r="E26" s="30" t="n"/>
+      <c r="E26" s="48" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="45" t="inlineStr">
@@ -8786,7 +8785,7 @@
           <t>La guardería</t>
         </is>
       </c>
-      <c r="E27" s="30" t="n"/>
+      <c r="E27" s="48" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="45" t="inlineStr">
@@ -8804,7 +8803,7 @@
           <t>Tu bróker o banco</t>
         </is>
       </c>
-      <c r="E28" s="30" t="n"/>
+      <c r="E28" s="48" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -8943,384 +8942,384 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>AGI (Adjusted Gross Income)</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>Ingreso bruto ajustado: tus ingresos totales menos algunos ajustes (la mitad del self-employment tax, aportes a IRA…). Decide muchos créditos y límites.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>Taxable income</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>Renta imponible: el AGI menos la deducción estándar o detallada y la QBI. Sobre ella se aplican los tramos.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>Standard deduction</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>Deducción estándar: una cantidad fija que restas sin justificar gastos. Casi todo el mundo la usa.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>Itemized deductions</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>Deducciones detalladas (Schedule A): hipoteca, impuestos estatales y locales, donativos… Solo conviene si suman más que la estándar.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>Filing status</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>Estado civil para declarar: single, married filing jointly, married filing separately, head of household.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>Head of household</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>Cabeza de familia: soltero que paga más de la mitad de los gastos de la casa de un dependiente. Tiene tramos y deducción mejores que single.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>Tax bracket</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>Tramo: cada parte de tu renta paga su tipo. Subir de tramo solo afecta a lo que pasa del límite.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>Marginal rate</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>Tipo marginal: el del último dólar que ganas.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="48" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>Effective rate</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>Tipo efectivo: impuesto total entre ingresos totales.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>Withholding</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>Retención: lo que tu empleador descuenta de cada cheque y manda al IRS por ti.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>W-4</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>Formulario que das a tu empleador para decidir cuánto te retiene.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="48" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>W-2</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>Resumen anual de salario y retenciones que te da cada empleador.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="48" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>1099-NEC</t>
         </is>
       </c>
-      <c r="C19" s="49" t="inlineStr">
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>Formulario de pagos a contratistas independientes (non-employee compensation).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>1099-K</t>
         </is>
       </c>
-      <c r="C20" s="49" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>Pagos recibidos por apps y plataformas de pago.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>Independent contractor</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="50" t="inlineStr">
         <is>
           <t>Contratista independiente: trabajas por tu cuenta; nadie te retiene y pagas el self-employment tax.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>Schedule C</t>
         </is>
       </c>
-      <c r="C22" s="49" t="inlineStr">
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>Anexo del 1040 donde declaras ingresos y gastos de tu negocio. Resultado: la ganancia neta.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="48" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>Schedule SE</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="50" t="inlineStr">
         <is>
           <t>Anexo donde calculas el self-employment tax.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>Self-employment tax</t>
         </is>
       </c>
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C24" s="50" t="inlineStr">
         <is>
           <t>Seguro Social (12.4%) y Medicare (2.9%) del trabajador por cuenta propia: pagas la parte del empleado y la del empleador. La mitad se resta del AGI.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>FICA</t>
         </is>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>Seguro Social (6.2%) y Medicare (1.45%) que se descuentan del cheque del empleado.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>QBI deduction</t>
         </is>
       </c>
-      <c r="C26" s="49" t="inlineStr">
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t>Deducción del 20% del ingreso calificado de negocio (sección 199A) para autónomos y pequeños negocios.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="48" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>Estimated tax (1040-ES)</t>
         </is>
       </c>
-      <c r="C27" s="49" t="inlineStr">
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>Pagos estimados: lo que pagas al IRS durante el año cuando no te retienen lo suficiente. Cuatro plazos al año.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="48" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>Safe harbor</t>
         </is>
       </c>
-      <c r="C28" s="49" t="inlineStr">
+      <c r="C28" s="50" t="inlineStr">
         <is>
           <t>Puerto seguro: si pagas a tiempo cierto mínimo (90% de este año o 100%/110% del año pasado), no hay multa aunque debas en abril.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="48" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>Underpayment penalty</t>
         </is>
       </c>
-      <c r="C29" s="49" t="inlineStr">
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <t>Multa por pagar poco o tarde durante el año (Form 2210).</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="48" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>Child Tax Credit (CTC)</t>
         </is>
       </c>
-      <c r="C30" s="49" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>Crédito por hijos menores de 17 con SSN. Resta directamente del impuesto.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="48" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>ACTC (Additional Child Tax Credit)</t>
         </is>
       </c>
-      <c r="C31" s="49" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t>Parte reembolsable del crédito por hijos: te la pagan aunque no debas impuesto.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="48" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>Credit for Other Dependents</t>
         </is>
       </c>
-      <c r="C32" s="49" t="inlineStr">
+      <c r="C32" s="50" t="inlineStr">
         <is>
           <t>Crédito de 500 $ por dependientes que no cumplen el CTC.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="48" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>Refund</t>
         </is>
       </c>
-      <c r="C33" s="49" t="inlineStr">
+      <c r="C33" s="50" t="inlineStr">
         <is>
           <t>Reembolso: lo que te devuelve el IRS si pagaste de más.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>Balance due</t>
         </is>
       </c>
-      <c r="C34" s="49" t="inlineStr">
+      <c r="C34" s="50" t="inlineStr">
         <is>
           <t>Lo que te toca pagar al declarar.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="48" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>EIN</t>
         </is>
       </c>
-      <c r="C35" s="49" t="inlineStr">
+      <c r="C35" s="50" t="inlineStr">
         <is>
           <t>Número de identificación de empleador; también lo usan algunos negocios propios.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>ITIN</t>
         </is>
       </c>
-      <c r="C36" s="49" t="inlineStr">
+      <c r="C36" s="50" t="inlineStr">
         <is>
           <t>Número de identificación del contribuyente para quien no puede tener SSN.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="48" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>Direct Pay / EFTPS</t>
         </is>
       </c>
-      <c r="C37" s="49" t="inlineStr">
+      <c r="C37" s="50" t="inlineStr">
         <is>
           <t>Formas oficiales de pagar al IRS por internet desde tu cuenta bancaria.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="48" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>Tax preparer</t>
         </is>
       </c>
-      <c r="C38" s="49" t="inlineStr">
+      <c r="C38" s="50" t="inlineStr">
         <is>
           <t>Preparador de impuestos. Exige que firme con su PTIN.</t>
         </is>
